--- a/Zinc/5. Cluster analysis/Typology Plots/Site_typology_sample_counts.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Site_typology_sample_counts.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -29,10 +29,10 @@
     <t xml:space="preserve">Main Stem</t>
   </si>
   <si>
-    <t xml:space="preserve">PD Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P Tribs</t>
+    <t xml:space="preserve">Developed Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
@@ -56,6 +56,18 @@
     <t xml:space="preserve">BSL3.3</t>
   </si>
   <si>
+    <t xml:space="preserve">BSL4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Downtown</t>
   </si>
   <si>
@@ -89,21 +101,30 @@
     <t xml:space="preserve">MCA3.1</t>
   </si>
   <si>
+    <t xml:space="preserve">MCA3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial Tribs</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCA4</t>
   </si>
   <si>
+    <t xml:space="preserve">MTN1.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">MTN4</t>
   </si>
   <si>
-    <t xml:space="preserve">NP Tribs</t>
-  </si>
-  <si>
     <t xml:space="preserve">NBO2</t>
   </si>
   <si>
     <t xml:space="preserve">NBO3</t>
   </si>
   <si>
+    <t xml:space="preserve">NBO5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pinhook Branch</t>
   </si>
   <si>
@@ -111,6 +132,9 @@
   </si>
   <si>
     <t xml:space="preserve">WBK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK3</t>
   </si>
 </sst>
 </file>
@@ -664,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
         <v>5</v>
@@ -675,81 +699,81 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -760,18 +784,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
@@ -782,40 +806,40 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -826,18 +850,18 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -848,18 +872,18 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -870,54 +894,54 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
         <v>8</v>
@@ -925,46 +949,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -975,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -983,21 +1007,21 @@
         <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -1005,86 +1029,262 @@
         <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B56" t="s">
         <v>5</v>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Zinc/5. Cluster analysis/Typology Plots/Site_typology_sample_counts.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Site_typology_sample_counts.xlsx
@@ -29,10 +29,10 @@
     <t xml:space="preserve">Main Stem</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
+    <t xml:space="preserve">Developed Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">BSL4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
+    <t xml:space="preserve">Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.2</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">MCA3.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
+    <t xml:space="preserve">Non-Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">MCA4</t>
